--- a/data/trans_orig/P79A4_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A4_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>765</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>53,25%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>606</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>606</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>606</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>606</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
